--- a/SP 2026 - predtekmovanje.xlsx
+++ b/SP 2026 - predtekmovanje.xlsx
@@ -1,24 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rihar\OneDrive\Dokumenti\Nogomet\Stave\SP2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rihar\Documents\SP2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{B413763D-BA23-4F86-8385-4F3120E8DB42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B88CB3C-69AC-4AA1-B5EB-4E71ED74860F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23136" yWindow="-744" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" calcMode="manual"/>
+  <calcPr calcId="191029" calcMode="manual"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -1798,34 +1809,19 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1851,6 +1847,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1887,7 +1898,7 @@
       <xdr:col>14</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>50</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:rowOff>64770</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1935,7 +1946,7 @@
       <xdr:col>15</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>67</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:rowOff>64770</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1983,7 +1994,7 @@
       <xdr:col>15</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>67</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:rowOff>64770</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2655,46 +2666,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
     </row>
     <row r="3" spans="1:23" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G3" s="28" t="s">
+      <c r="G3" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="28"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
-      <c r="L3" s="29"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
+      <c r="L3" s="38"/>
     </row>
     <row r="5" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L5" s="1" t="s">
@@ -2702,7 +2713,7 @@
       </c>
     </row>
     <row r="6" spans="1:23" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="25" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="6">
@@ -2733,7 +2744,7 @@
       <c r="K6" s="14"/>
     </row>
     <row r="7" spans="1:23" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="24"/>
+      <c r="A7" s="25"/>
       <c r="B7" s="6">
         <v>46185</v>
       </c>
@@ -2763,7 +2774,7 @@
       <c r="W7" s="3"/>
     </row>
     <row r="8" spans="1:23" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="24"/>
+      <c r="A8" s="25"/>
       <c r="B8" s="6">
         <v>46191</v>
       </c>
@@ -2792,7 +2803,7 @@
       <c r="K8" s="14"/>
     </row>
     <row r="9" spans="1:23" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="24"/>
+      <c r="A9" s="25"/>
       <c r="B9" s="6">
         <v>46192</v>
       </c>
@@ -2821,7 +2832,7 @@
       <c r="K9" s="14"/>
     </row>
     <row r="10" spans="1:23" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="24"/>
+      <c r="A10" s="25"/>
       <c r="B10" s="6">
         <v>46198</v>
       </c>
@@ -2850,7 +2861,7 @@
       <c r="K10" s="14"/>
     </row>
     <row r="11" spans="1:23" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="24"/>
+      <c r="A11" s="25"/>
       <c r="B11" s="6">
         <v>46198</v>
       </c>
@@ -2882,7 +2893,7 @@
       <c r="C12" s="23"/>
     </row>
     <row r="13" spans="1:23" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="25" t="s">
         <v>5</v>
       </c>
       <c r="B13" s="6">
@@ -2913,7 +2924,7 @@
       <c r="K13" s="14"/>
     </row>
     <row r="14" spans="1:23" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="24"/>
+      <c r="A14" s="25"/>
       <c r="B14" s="6">
         <v>46186</v>
       </c>
@@ -2942,7 +2953,7 @@
       <c r="K14" s="14"/>
     </row>
     <row r="15" spans="1:23" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="24"/>
+      <c r="A15" s="25"/>
       <c r="B15" s="6">
         <v>46191</v>
       </c>
@@ -2971,7 +2982,7 @@
       <c r="K15" s="14"/>
     </row>
     <row r="16" spans="1:23" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="24"/>
+      <c r="A16" s="25"/>
       <c r="B16" s="6">
         <v>46192</v>
       </c>
@@ -3000,7 +3011,7 @@
       <c r="K16" s="14"/>
     </row>
     <row r="17" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="24"/>
+      <c r="A17" s="25"/>
       <c r="B17" s="6">
         <v>46197</v>
       </c>
@@ -3029,7 +3040,7 @@
       <c r="K17" s="14"/>
     </row>
     <row r="18" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="24"/>
+      <c r="A18" s="25"/>
       <c r="B18" s="6">
         <v>46197</v>
       </c>
@@ -3061,7 +3072,7 @@
       <c r="C19" s="23"/>
     </row>
     <row r="20" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="24" t="s">
+      <c r="A20" s="25" t="s">
         <v>6</v>
       </c>
       <c r="B20" s="6">
@@ -3092,7 +3103,7 @@
       <c r="K20" s="14"/>
     </row>
     <row r="21" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="24"/>
+      <c r="A21" s="25"/>
       <c r="B21" s="6">
         <v>46187</v>
       </c>
@@ -3121,7 +3132,7 @@
       <c r="K21" s="14"/>
     </row>
     <row r="22" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="24"/>
+      <c r="A22" s="25"/>
       <c r="B22" s="6">
         <v>46193</v>
       </c>
@@ -3150,7 +3161,7 @@
       <c r="K22" s="14"/>
     </row>
     <row r="23" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="24"/>
+      <c r="A23" s="25"/>
       <c r="B23" s="6">
         <v>46193</v>
       </c>
@@ -3179,7 +3190,7 @@
       <c r="K23" s="14"/>
     </row>
     <row r="24" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="24"/>
+      <c r="A24" s="25"/>
       <c r="B24" s="6">
         <v>46198</v>
       </c>
@@ -3208,7 +3219,7 @@
       <c r="K24" s="14"/>
     </row>
     <row r="25" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="24"/>
+      <c r="A25" s="25"/>
       <c r="B25" s="6">
         <v>46198</v>
       </c>
@@ -3240,7 +3251,7 @@
       <c r="C26" s="23"/>
     </row>
     <row r="27" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="24" t="s">
+      <c r="A27" s="25" t="s">
         <v>7</v>
       </c>
       <c r="B27" s="6">
@@ -3271,7 +3282,7 @@
       <c r="K27" s="14"/>
     </row>
     <row r="28" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="24"/>
+      <c r="A28" s="25"/>
       <c r="B28" s="6">
         <v>46187</v>
       </c>
@@ -3300,7 +3311,7 @@
       <c r="K28" s="14"/>
     </row>
     <row r="29" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="24"/>
+      <c r="A29" s="25"/>
       <c r="B29" s="6">
         <v>46192</v>
       </c>
@@ -3329,7 +3340,7 @@
       <c r="K29" s="14"/>
     </row>
     <row r="30" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="24"/>
+      <c r="A30" s="25"/>
       <c r="B30" s="6">
         <v>46193</v>
       </c>
@@ -3358,7 +3369,7 @@
       <c r="K30" s="14"/>
     </row>
     <row r="31" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="24"/>
+      <c r="A31" s="25"/>
       <c r="B31" s="6">
         <v>45469</v>
       </c>
@@ -3387,7 +3398,7 @@
       <c r="K31" s="14"/>
     </row>
     <row r="32" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="24"/>
+      <c r="A32" s="25"/>
       <c r="B32" s="6">
         <v>45469</v>
       </c>
@@ -3419,7 +3430,7 @@
       <c r="C33" s="23"/>
     </row>
     <row r="34" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="24" t="s">
+      <c r="A34" s="25" t="s">
         <v>8</v>
       </c>
       <c r="B34" s="6">
@@ -3450,7 +3461,7 @@
       <c r="K34" s="14"/>
     </row>
     <row r="35" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="24"/>
+      <c r="A35" s="25"/>
       <c r="B35" s="6">
         <v>46188</v>
       </c>
@@ -3479,7 +3490,7 @@
       <c r="K35" s="14"/>
     </row>
     <row r="36" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="24"/>
+      <c r="A36" s="25"/>
       <c r="B36" s="6">
         <v>46193</v>
       </c>
@@ -3508,7 +3519,7 @@
       <c r="K36" s="14"/>
     </row>
     <row r="37" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="24"/>
+      <c r="A37" s="25"/>
       <c r="B37" s="6">
         <v>45464</v>
       </c>
@@ -3537,7 +3548,7 @@
       <c r="K37" s="14"/>
     </row>
     <row r="38" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="24"/>
+      <c r="A38" s="25"/>
       <c r="B38" s="6">
         <v>46198</v>
       </c>
@@ -3566,7 +3577,7 @@
       <c r="K38" s="14"/>
     </row>
     <row r="39" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="24"/>
+      <c r="A39" s="25"/>
       <c r="B39" s="6">
         <v>46198</v>
       </c>
@@ -3598,7 +3609,7 @@
       <c r="C40" s="23"/>
     </row>
     <row r="41" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="24" t="s">
+      <c r="A41" s="25" t="s">
         <v>9</v>
       </c>
       <c r="B41" s="6">
@@ -3629,7 +3640,7 @@
       <c r="K41" s="14"/>
     </row>
     <row r="42" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="24"/>
+      <c r="A42" s="25"/>
       <c r="B42" s="6">
         <v>46188</v>
       </c>
@@ -3658,7 +3669,7 @@
       <c r="K42" s="14"/>
     </row>
     <row r="43" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="24"/>
+      <c r="A43" s="25"/>
       <c r="B43" s="6">
         <v>46193</v>
       </c>
@@ -3687,7 +3698,7 @@
       <c r="K43" s="14"/>
     </row>
     <row r="44" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="24"/>
+      <c r="A44" s="25"/>
       <c r="B44" s="6">
         <v>45464</v>
       </c>
@@ -3716,7 +3727,7 @@
       <c r="K44" s="14"/>
     </row>
     <row r="45" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="24"/>
+      <c r="A45" s="25"/>
       <c r="B45" s="6">
         <v>46199</v>
       </c>
@@ -3745,7 +3756,7 @@
       <c r="K45" s="14"/>
     </row>
     <row r="46" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="24"/>
+      <c r="A46" s="25"/>
       <c r="B46" s="6">
         <v>46199</v>
       </c>
@@ -3783,7 +3794,7 @@
       </c>
     </row>
     <row r="48" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="24" t="s">
+      <c r="A48" s="25" t="s">
         <v>66</v>
       </c>
       <c r="B48" s="6">
@@ -3814,7 +3825,7 @@
       <c r="K48" s="14"/>
     </row>
     <row r="49" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="24"/>
+      <c r="A49" s="25"/>
       <c r="B49" s="6">
         <v>46189</v>
       </c>
@@ -3843,7 +3854,7 @@
       <c r="K49" s="14"/>
     </row>
     <row r="50" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="24"/>
+      <c r="A50" s="25"/>
       <c r="B50" s="6">
         <v>46194</v>
       </c>
@@ -3872,7 +3883,7 @@
       <c r="K50" s="14"/>
     </row>
     <row r="51" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="24"/>
+      <c r="A51" s="25"/>
       <c r="B51" s="6">
         <v>46195</v>
       </c>
@@ -3901,7 +3912,7 @@
       <c r="K51" s="14"/>
     </row>
     <row r="52" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="24"/>
+      <c r="A52" s="25"/>
       <c r="B52" s="6">
         <v>46200</v>
       </c>
@@ -3930,7 +3941,7 @@
       <c r="K52" s="14"/>
     </row>
     <row r="53" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="24"/>
+      <c r="A53" s="25"/>
       <c r="B53" s="6">
         <v>46200</v>
       </c>
@@ -3962,7 +3973,7 @@
       <c r="C54" s="23"/>
     </row>
     <row r="55" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="24" t="s">
+      <c r="A55" s="25" t="s">
         <v>67</v>
       </c>
       <c r="B55" s="6">
@@ -3993,7 +4004,7 @@
       <c r="K55" s="14"/>
     </row>
     <row r="56" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="24"/>
+      <c r="A56" s="25"/>
       <c r="B56" s="6">
         <v>46189</v>
       </c>
@@ -4022,7 +4033,7 @@
       <c r="K56" s="14"/>
     </row>
     <row r="57" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="24"/>
+      <c r="A57" s="25"/>
       <c r="B57" s="6">
         <v>46194</v>
       </c>
@@ -4051,7 +4062,7 @@
       <c r="K57" s="14"/>
     </row>
     <row r="58" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="24"/>
+      <c r="A58" s="25"/>
       <c r="B58" s="6">
         <v>46195</v>
       </c>
@@ -4080,7 +4091,7 @@
       <c r="K58" s="14"/>
     </row>
     <row r="59" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="24"/>
+      <c r="A59" s="25"/>
       <c r="B59" s="6">
         <v>46200</v>
       </c>
@@ -4109,7 +4120,7 @@
       <c r="K59" s="14"/>
     </row>
     <row r="60" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="24"/>
+      <c r="A60" s="25"/>
       <c r="B60" s="6">
         <v>46200</v>
       </c>
@@ -4141,7 +4152,7 @@
       <c r="C61" s="23"/>
     </row>
     <row r="62" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="24" t="s">
+      <c r="A62" s="25" t="s">
         <v>72</v>
       </c>
       <c r="B62" s="6">
@@ -4172,7 +4183,7 @@
       <c r="K62" s="14"/>
     </row>
     <row r="63" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="24"/>
+      <c r="A63" s="25"/>
       <c r="B63" s="6">
         <v>46190</v>
       </c>
@@ -4201,7 +4212,7 @@
       <c r="K63" s="14"/>
     </row>
     <row r="64" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="24"/>
+      <c r="A64" s="25"/>
       <c r="B64" s="6">
         <v>46195</v>
       </c>
@@ -4230,7 +4241,7 @@
       <c r="K64" s="14"/>
     </row>
     <row r="65" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="24"/>
+      <c r="A65" s="25"/>
       <c r="B65" s="6">
         <v>46196</v>
       </c>
@@ -4259,7 +4270,7 @@
       <c r="K65" s="14"/>
     </row>
     <row r="66" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="24"/>
+      <c r="A66" s="25"/>
       <c r="B66" s="6">
         <v>46199</v>
       </c>
@@ -4288,7 +4299,7 @@
       <c r="K66" s="14"/>
     </row>
     <row r="67" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="24"/>
+      <c r="A67" s="25"/>
       <c r="B67" s="6">
         <v>46199</v>
       </c>
@@ -4320,7 +4331,7 @@
       <c r="C68" s="23"/>
     </row>
     <row r="69" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="24" t="s">
+      <c r="A69" s="25" t="s">
         <v>82</v>
       </c>
       <c r="B69" s="6">
@@ -4351,7 +4362,7 @@
       <c r="K69" s="14"/>
     </row>
     <row r="70" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="24"/>
+      <c r="A70" s="25"/>
       <c r="B70" s="6">
         <v>46190</v>
       </c>
@@ -4380,7 +4391,7 @@
       <c r="K70" s="14"/>
     </row>
     <row r="71" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="24"/>
+      <c r="A71" s="25"/>
       <c r="B71" s="6">
         <v>46195</v>
       </c>
@@ -4409,7 +4420,7 @@
       <c r="K71" s="14"/>
     </row>
     <row r="72" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="24"/>
+      <c r="A72" s="25"/>
       <c r="B72" s="6">
         <v>46196</v>
       </c>
@@ -4438,7 +4449,7 @@
       <c r="K72" s="14"/>
     </row>
     <row r="73" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="24"/>
+      <c r="A73" s="25"/>
       <c r="B73" s="6">
         <v>46201</v>
       </c>
@@ -4467,7 +4478,7 @@
       <c r="K73" s="14"/>
     </row>
     <row r="74" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="24"/>
+      <c r="A74" s="25"/>
       <c r="B74" s="6">
         <v>46201</v>
       </c>
@@ -4499,7 +4510,7 @@
       <c r="C75" s="23"/>
     </row>
     <row r="76" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="24" t="s">
+      <c r="A76" s="25" t="s">
         <v>83</v>
       </c>
       <c r="B76" s="6">
@@ -4530,7 +4541,7 @@
       <c r="K76" s="14"/>
     </row>
     <row r="77" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="24"/>
+      <c r="A77" s="25"/>
       <c r="B77" s="6">
         <v>46191</v>
       </c>
@@ -4559,7 +4570,7 @@
       <c r="K77" s="14"/>
     </row>
     <row r="78" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="24"/>
+      <c r="A78" s="25"/>
       <c r="B78" s="6">
         <v>46196</v>
       </c>
@@ -4588,7 +4599,7 @@
       <c r="K78" s="14"/>
     </row>
     <row r="79" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="24"/>
+      <c r="A79" s="25"/>
       <c r="B79" s="6">
         <v>46197</v>
       </c>
@@ -4617,7 +4628,7 @@
       <c r="K79" s="14"/>
     </row>
     <row r="80" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="24"/>
+      <c r="A80" s="25"/>
       <c r="B80" s="6">
         <v>46201</v>
       </c>
@@ -4646,7 +4657,7 @@
       <c r="K80" s="14"/>
     </row>
     <row r="81" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="24"/>
+      <c r="A81" s="25"/>
       <c r="B81" s="6">
         <v>46201</v>
       </c>
@@ -4678,7 +4689,7 @@
       <c r="C82" s="23"/>
     </row>
     <row r="83" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="24" t="s">
+      <c r="A83" s="25" t="s">
         <v>84</v>
       </c>
       <c r="B83" s="6">
@@ -4709,7 +4720,7 @@
       <c r="K83" s="14"/>
     </row>
     <row r="84" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="24"/>
+      <c r="A84" s="25"/>
       <c r="B84" s="6">
         <v>46191</v>
       </c>
@@ -4738,7 +4749,7 @@
       <c r="K84" s="14"/>
     </row>
     <row r="85" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="24"/>
+      <c r="A85" s="25"/>
       <c r="B85" s="6">
         <v>46196</v>
       </c>
@@ -4767,7 +4778,7 @@
       <c r="K85" s="14"/>
     </row>
     <row r="86" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="24"/>
+      <c r="A86" s="25"/>
       <c r="B86" s="6">
         <v>46197</v>
       </c>
@@ -4796,7 +4807,7 @@
       <c r="K86" s="14"/>
     </row>
     <row r="87" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="24"/>
+      <c r="A87" s="25"/>
       <c r="B87" s="6">
         <v>46200</v>
       </c>
@@ -4825,7 +4836,7 @@
       <c r="K87" s="14"/>
     </row>
     <row r="88" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="24"/>
+      <c r="A88" s="25"/>
       <c r="B88" s="6">
         <v>46200</v>
       </c>
@@ -4854,27 +4865,27 @@
       <c r="K88" s="14"/>
     </row>
     <row r="89" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="H89" s="28" t="s">
+      <c r="H89" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="I89" s="28"/>
-      <c r="J89" s="29"/>
-      <c r="K89" s="29"/>
-      <c r="L89" s="29"/>
-      <c r="M89" s="29"/>
+      <c r="I89" s="37"/>
+      <c r="J89" s="38"/>
+      <c r="K89" s="38"/>
+      <c r="L89" s="38"/>
+      <c r="M89" s="38"/>
     </row>
     <row r="90" spans="1:13" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B90" s="30" t="s">
+      <c r="B90" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="C90" s="30"/>
-      <c r="D90" s="30"/>
-    </row>
-    <row r="92" spans="1:13" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B92" s="32" t="s">
+      <c r="C90" s="39"/>
+      <c r="D90" s="39"/>
+    </row>
+    <row r="92" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B92" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="C92" s="32"/>
+      <c r="C92" s="27"/>
       <c r="D92" s="2"/>
       <c r="E92" s="2"/>
       <c r="G92" s="12" t="s">
@@ -4887,20 +4898,20 @@
       <c r="B93" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C93" s="33"/>
-      <c r="D93" s="33"/>
-      <c r="E93" s="33"/>
+      <c r="C93" s="24"/>
+      <c r="D93" s="24"/>
+      <c r="E93" s="24"/>
       <c r="F93" s="13">
         <v>2</v>
       </c>
       <c r="G93" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="H93" s="33"/>
-      <c r="I93" s="33"/>
-      <c r="J93" s="33"/>
-      <c r="K93" s="33"/>
-      <c r="L93" s="33"/>
+      <c r="H93" s="26"/>
+      <c r="I93" s="26"/>
+      <c r="J93" s="26"/>
+      <c r="K93" s="26"/>
+      <c r="L93" s="26"/>
       <c r="M93" s="13">
         <v>2</v>
       </c>
@@ -4909,20 +4920,17 @@
       <c r="B94" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C94" s="31"/>
-      <c r="D94" s="31"/>
-      <c r="E94" s="31"/>
       <c r="F94" s="13">
         <v>2</v>
       </c>
       <c r="G94" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="H94" s="31"/>
-      <c r="I94" s="31"/>
-      <c r="J94" s="31"/>
-      <c r="K94" s="31"/>
-      <c r="L94" s="31"/>
+      <c r="H94" s="24"/>
+      <c r="I94" s="24"/>
+      <c r="J94" s="24"/>
+      <c r="K94" s="24"/>
+      <c r="L94" s="24"/>
       <c r="M94" s="13">
         <v>2</v>
       </c>
@@ -4931,20 +4939,20 @@
       <c r="B95" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C95" s="31"/>
-      <c r="D95" s="31"/>
-      <c r="E95" s="31"/>
+      <c r="C95" s="24"/>
+      <c r="D95" s="24"/>
+      <c r="E95" s="24"/>
       <c r="F95" s="13">
         <v>2</v>
       </c>
       <c r="G95" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H95" s="31"/>
-      <c r="I95" s="31"/>
-      <c r="J95" s="31"/>
-      <c r="K95" s="31"/>
-      <c r="L95" s="31"/>
+      <c r="H95" s="24"/>
+      <c r="I95" s="24"/>
+      <c r="J95" s="24"/>
+      <c r="K95" s="24"/>
+      <c r="L95" s="24"/>
       <c r="M95" s="13">
         <v>2</v>
       </c>
@@ -4953,20 +4961,20 @@
       <c r="B96" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C96" s="31"/>
-      <c r="D96" s="31"/>
-      <c r="E96" s="31"/>
+      <c r="C96" s="24"/>
+      <c r="D96" s="24"/>
+      <c r="E96" s="24"/>
       <c r="F96" s="13">
         <v>2</v>
       </c>
       <c r="G96" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="H96" s="31"/>
-      <c r="I96" s="31"/>
-      <c r="J96" s="31"/>
-      <c r="K96" s="31"/>
-      <c r="L96" s="31"/>
+      <c r="H96" s="24"/>
+      <c r="I96" s="24"/>
+      <c r="J96" s="24"/>
+      <c r="K96" s="24"/>
+      <c r="L96" s="24"/>
       <c r="M96" s="13">
         <v>2</v>
       </c>
@@ -4979,10 +4987,10 @@
       <c r="L97" s="2"/>
     </row>
     <row r="98" spans="2:13" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B98" s="32" t="s">
+      <c r="B98" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="C98" s="32"/>
+      <c r="C98" s="27"/>
       <c r="D98" s="2"/>
       <c r="E98" s="2"/>
       <c r="G98" s="12" t="s">
@@ -4998,20 +5006,20 @@
       <c r="B99" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C99" s="33"/>
-      <c r="D99" s="33"/>
-      <c r="E99" s="33"/>
+      <c r="C99" s="26"/>
+      <c r="D99" s="26"/>
+      <c r="E99" s="26"/>
       <c r="F99" s="13">
         <v>2</v>
       </c>
       <c r="G99" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="H99" s="33"/>
-      <c r="I99" s="33"/>
-      <c r="J99" s="33"/>
-      <c r="K99" s="33"/>
-      <c r="L99" s="33"/>
+      <c r="H99" s="26"/>
+      <c r="I99" s="26"/>
+      <c r="J99" s="26"/>
+      <c r="K99" s="26"/>
+      <c r="L99" s="26"/>
       <c r="M99" s="13">
         <v>2</v>
       </c>
@@ -5020,20 +5028,20 @@
       <c r="B100" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C100" s="31"/>
-      <c r="D100" s="31"/>
-      <c r="E100" s="31"/>
+      <c r="C100" s="24"/>
+      <c r="D100" s="24"/>
+      <c r="E100" s="24"/>
       <c r="F100" s="13">
         <v>2</v>
       </c>
       <c r="G100" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="H100" s="33"/>
-      <c r="I100" s="33"/>
-      <c r="J100" s="33"/>
-      <c r="K100" s="33"/>
-      <c r="L100" s="33"/>
+      <c r="H100" s="26"/>
+      <c r="I100" s="26"/>
+      <c r="J100" s="26"/>
+      <c r="K100" s="26"/>
+      <c r="L100" s="26"/>
       <c r="M100" s="13">
         <v>2</v>
       </c>
@@ -5042,20 +5050,20 @@
       <c r="B101" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C101" s="31"/>
-      <c r="D101" s="31"/>
-      <c r="E101" s="31"/>
+      <c r="C101" s="24"/>
+      <c r="D101" s="24"/>
+      <c r="E101" s="24"/>
       <c r="F101" s="13">
         <v>2</v>
       </c>
       <c r="G101" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H101" s="33"/>
-      <c r="I101" s="33"/>
-      <c r="J101" s="33"/>
-      <c r="K101" s="33"/>
-      <c r="L101" s="33"/>
+      <c r="H101" s="26"/>
+      <c r="I101" s="26"/>
+      <c r="J101" s="26"/>
+      <c r="K101" s="26"/>
+      <c r="L101" s="26"/>
       <c r="M101" s="13">
         <v>2</v>
       </c>
@@ -5064,20 +5072,20 @@
       <c r="B102" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C102" s="31"/>
-      <c r="D102" s="31"/>
-      <c r="E102" s="31"/>
+      <c r="C102" s="24"/>
+      <c r="D102" s="24"/>
+      <c r="E102" s="24"/>
       <c r="F102" s="13">
         <v>2</v>
       </c>
       <c r="G102" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="H102" s="33"/>
-      <c r="I102" s="33"/>
-      <c r="J102" s="33"/>
-      <c r="K102" s="33"/>
-      <c r="L102" s="33"/>
+      <c r="H102" s="26"/>
+      <c r="I102" s="26"/>
+      <c r="J102" s="26"/>
+      <c r="K102" s="26"/>
+      <c r="L102" s="26"/>
       <c r="M102" s="13">
         <v>2</v>
       </c>
@@ -5090,10 +5098,10 @@
       <c r="L103" s="2"/>
     </row>
     <row r="104" spans="2:13" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B104" s="32" t="s">
+      <c r="B104" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="C104" s="32"/>
+      <c r="C104" s="27"/>
       <c r="D104" s="2"/>
       <c r="E104" s="2"/>
       <c r="G104" s="12" t="s">
@@ -5109,20 +5117,20 @@
       <c r="B105" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C105" s="33"/>
-      <c r="D105" s="33"/>
-      <c r="E105" s="33"/>
+      <c r="C105" s="26"/>
+      <c r="D105" s="26"/>
+      <c r="E105" s="26"/>
       <c r="F105" s="13">
         <v>2</v>
       </c>
       <c r="G105" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="H105" s="33"/>
-      <c r="I105" s="33"/>
-      <c r="J105" s="33"/>
-      <c r="K105" s="33"/>
-      <c r="L105" s="33"/>
+      <c r="H105" s="26"/>
+      <c r="I105" s="26"/>
+      <c r="J105" s="26"/>
+      <c r="K105" s="26"/>
+      <c r="L105" s="26"/>
       <c r="M105" s="13">
         <v>2</v>
       </c>
@@ -5131,20 +5139,20 @@
       <c r="B106" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C106" s="31"/>
-      <c r="D106" s="31"/>
-      <c r="E106" s="31"/>
+      <c r="C106" s="24"/>
+      <c r="D106" s="24"/>
+      <c r="E106" s="24"/>
       <c r="F106" s="13">
         <v>2</v>
       </c>
       <c r="G106" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="H106" s="33"/>
-      <c r="I106" s="33"/>
-      <c r="J106" s="33"/>
-      <c r="K106" s="33"/>
-      <c r="L106" s="33"/>
+      <c r="H106" s="26"/>
+      <c r="I106" s="26"/>
+      <c r="J106" s="26"/>
+      <c r="K106" s="26"/>
+      <c r="L106" s="26"/>
       <c r="M106" s="13">
         <v>2</v>
       </c>
@@ -5153,20 +5161,20 @@
       <c r="B107" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C107" s="31"/>
-      <c r="D107" s="31"/>
-      <c r="E107" s="31"/>
+      <c r="C107" s="24"/>
+      <c r="D107" s="24"/>
+      <c r="E107" s="24"/>
       <c r="F107" s="13">
         <v>2</v>
       </c>
       <c r="G107" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H107" s="33"/>
-      <c r="I107" s="33"/>
-      <c r="J107" s="33"/>
-      <c r="K107" s="33"/>
-      <c r="L107" s="33"/>
+      <c r="H107" s="26"/>
+      <c r="I107" s="26"/>
+      <c r="J107" s="26"/>
+      <c r="K107" s="26"/>
+      <c r="L107" s="26"/>
       <c r="M107" s="13">
         <v>2</v>
       </c>
@@ -5175,29 +5183,29 @@
       <c r="B108" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C108" s="31"/>
-      <c r="D108" s="31"/>
-      <c r="E108" s="31"/>
+      <c r="C108" s="24"/>
+      <c r="D108" s="24"/>
+      <c r="E108" s="24"/>
       <c r="F108" s="13">
         <v>2</v>
       </c>
       <c r="G108" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="H108" s="33"/>
-      <c r="I108" s="33"/>
-      <c r="J108" s="33"/>
-      <c r="K108" s="33"/>
-      <c r="L108" s="33"/>
+      <c r="H108" s="26"/>
+      <c r="I108" s="26"/>
+      <c r="J108" s="26"/>
+      <c r="K108" s="26"/>
+      <c r="L108" s="26"/>
       <c r="M108" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="110" spans="2:13" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B110" s="32" t="s">
+      <c r="B110" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C110" s="32"/>
+      <c r="C110" s="27"/>
       <c r="D110" s="2"/>
       <c r="E110" s="2"/>
       <c r="G110" s="12" t="s">
@@ -5210,20 +5218,20 @@
       <c r="B111" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C111" s="33"/>
-      <c r="D111" s="33"/>
-      <c r="E111" s="33"/>
+      <c r="C111" s="26"/>
+      <c r="D111" s="26"/>
+      <c r="E111" s="26"/>
       <c r="F111" s="13">
         <v>2</v>
       </c>
       <c r="G111" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="H111" s="33"/>
-      <c r="I111" s="33"/>
-      <c r="J111" s="33"/>
-      <c r="K111" s="33"/>
-      <c r="L111" s="33"/>
+      <c r="H111" s="26"/>
+      <c r="I111" s="26"/>
+      <c r="J111" s="26"/>
+      <c r="K111" s="26"/>
+      <c r="L111" s="26"/>
       <c r="M111" s="13">
         <v>2</v>
       </c>
@@ -5232,20 +5240,20 @@
       <c r="B112" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C112" s="31"/>
-      <c r="D112" s="31"/>
-      <c r="E112" s="31"/>
+      <c r="C112" s="24"/>
+      <c r="D112" s="24"/>
+      <c r="E112" s="24"/>
       <c r="F112" s="13">
         <v>2</v>
       </c>
       <c r="G112" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="H112" s="31"/>
-      <c r="I112" s="31"/>
-      <c r="J112" s="31"/>
-      <c r="K112" s="31"/>
-      <c r="L112" s="31"/>
+      <c r="H112" s="24"/>
+      <c r="I112" s="24"/>
+      <c r="J112" s="24"/>
+      <c r="K112" s="24"/>
+      <c r="L112" s="24"/>
       <c r="M112" s="13">
         <v>2</v>
       </c>
@@ -5254,20 +5262,20 @@
       <c r="B113" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C113" s="31"/>
-      <c r="D113" s="31"/>
-      <c r="E113" s="31"/>
+      <c r="C113" s="24"/>
+      <c r="D113" s="24"/>
+      <c r="E113" s="24"/>
       <c r="F113" s="13">
         <v>2</v>
       </c>
       <c r="G113" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H113" s="31"/>
-      <c r="I113" s="31"/>
-      <c r="J113" s="31"/>
-      <c r="K113" s="31"/>
-      <c r="L113" s="31"/>
+      <c r="H113" s="24"/>
+      <c r="I113" s="24"/>
+      <c r="J113" s="24"/>
+      <c r="K113" s="24"/>
+      <c r="L113" s="24"/>
       <c r="M113" s="13">
         <v>2</v>
       </c>
@@ -5276,29 +5284,29 @@
       <c r="B114" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C114" s="31"/>
-      <c r="D114" s="31"/>
-      <c r="E114" s="31"/>
+      <c r="C114" s="24"/>
+      <c r="D114" s="24"/>
+      <c r="E114" s="24"/>
       <c r="F114" s="13">
         <v>2</v>
       </c>
       <c r="G114" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="H114" s="31"/>
-      <c r="I114" s="31"/>
-      <c r="J114" s="31"/>
-      <c r="K114" s="31"/>
-      <c r="L114" s="31"/>
+      <c r="H114" s="24"/>
+      <c r="I114" s="24"/>
+      <c r="J114" s="24"/>
+      <c r="K114" s="24"/>
+      <c r="L114" s="24"/>
       <c r="M114" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="116" spans="2:13" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B116" s="32" t="s">
+      <c r="B116" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="C116" s="32"/>
+      <c r="C116" s="27"/>
       <c r="D116" s="2"/>
       <c r="E116" s="2"/>
       <c r="G116" s="12" t="s">
@@ -5311,20 +5319,20 @@
       <c r="B117" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C117" s="33"/>
-      <c r="D117" s="33"/>
-      <c r="E117" s="33"/>
+      <c r="C117" s="26"/>
+      <c r="D117" s="26"/>
+      <c r="E117" s="26"/>
       <c r="F117" s="13">
         <v>2</v>
       </c>
       <c r="G117" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="H117" s="33"/>
-      <c r="I117" s="33"/>
-      <c r="J117" s="33"/>
-      <c r="K117" s="33"/>
-      <c r="L117" s="33"/>
+      <c r="H117" s="26"/>
+      <c r="I117" s="26"/>
+      <c r="J117" s="26"/>
+      <c r="K117" s="26"/>
+      <c r="L117" s="26"/>
       <c r="M117" s="13">
         <v>2</v>
       </c>
@@ -5333,20 +5341,20 @@
       <c r="B118" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C118" s="31"/>
-      <c r="D118" s="31"/>
-      <c r="E118" s="31"/>
+      <c r="C118" s="24"/>
+      <c r="D118" s="24"/>
+      <c r="E118" s="24"/>
       <c r="F118" s="13">
         <v>2</v>
       </c>
       <c r="G118" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="H118" s="31"/>
-      <c r="I118" s="31"/>
-      <c r="J118" s="31"/>
-      <c r="K118" s="31"/>
-      <c r="L118" s="31"/>
+      <c r="H118" s="24"/>
+      <c r="I118" s="24"/>
+      <c r="J118" s="24"/>
+      <c r="K118" s="24"/>
+      <c r="L118" s="24"/>
       <c r="M118" s="13">
         <v>2</v>
       </c>
@@ -5355,20 +5363,20 @@
       <c r="B119" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C119" s="31"/>
-      <c r="D119" s="31"/>
-      <c r="E119" s="31"/>
+      <c r="C119" s="24"/>
+      <c r="D119" s="24"/>
+      <c r="E119" s="24"/>
       <c r="F119" s="13">
         <v>2</v>
       </c>
       <c r="G119" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H119" s="31"/>
-      <c r="I119" s="31"/>
-      <c r="J119" s="31"/>
-      <c r="K119" s="31"/>
-      <c r="L119" s="31"/>
+      <c r="H119" s="24"/>
+      <c r="I119" s="24"/>
+      <c r="J119" s="24"/>
+      <c r="K119" s="24"/>
+      <c r="L119" s="24"/>
       <c r="M119" s="13">
         <v>2</v>
       </c>
@@ -5377,29 +5385,29 @@
       <c r="B120" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C120" s="31"/>
-      <c r="D120" s="31"/>
-      <c r="E120" s="31"/>
+      <c r="C120" s="24"/>
+      <c r="D120" s="24"/>
+      <c r="E120" s="24"/>
       <c r="F120" s="13">
         <v>2</v>
       </c>
       <c r="G120" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="H120" s="31"/>
-      <c r="I120" s="31"/>
-      <c r="J120" s="31"/>
-      <c r="K120" s="31"/>
-      <c r="L120" s="31"/>
+      <c r="H120" s="24"/>
+      <c r="I120" s="24"/>
+      <c r="J120" s="24"/>
+      <c r="K120" s="24"/>
+      <c r="L120" s="24"/>
       <c r="M120" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="122" spans="2:13" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B122" s="32" t="s">
+      <c r="B122" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="C122" s="32"/>
+      <c r="C122" s="27"/>
       <c r="D122" s="2"/>
       <c r="E122" s="2"/>
       <c r="G122" s="12" t="s">
@@ -5412,20 +5420,20 @@
       <c r="B123" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C123" s="33"/>
-      <c r="D123" s="33"/>
-      <c r="E123" s="33"/>
+      <c r="C123" s="26"/>
+      <c r="D123" s="26"/>
+      <c r="E123" s="26"/>
       <c r="F123" s="13">
         <v>2</v>
       </c>
       <c r="G123" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="H123" s="33"/>
-      <c r="I123" s="33"/>
-      <c r="J123" s="33"/>
-      <c r="K123" s="33"/>
-      <c r="L123" s="33"/>
+      <c r="H123" s="26"/>
+      <c r="I123" s="26"/>
+      <c r="J123" s="26"/>
+      <c r="K123" s="26"/>
+      <c r="L123" s="26"/>
       <c r="M123" s="13">
         <v>2</v>
       </c>
@@ -5434,20 +5442,20 @@
       <c r="B124" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C124" s="31"/>
-      <c r="D124" s="31"/>
-      <c r="E124" s="31"/>
+      <c r="C124" s="24"/>
+      <c r="D124" s="24"/>
+      <c r="E124" s="24"/>
       <c r="F124" s="13">
         <v>2</v>
       </c>
       <c r="G124" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="H124" s="31"/>
-      <c r="I124" s="31"/>
-      <c r="J124" s="31"/>
-      <c r="K124" s="31"/>
-      <c r="L124" s="31"/>
+      <c r="H124" s="24"/>
+      <c r="I124" s="24"/>
+      <c r="J124" s="24"/>
+      <c r="K124" s="24"/>
+      <c r="L124" s="24"/>
       <c r="M124" s="13">
         <v>2</v>
       </c>
@@ -5456,20 +5464,20 @@
       <c r="B125" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C125" s="31"/>
-      <c r="D125" s="31"/>
-      <c r="E125" s="31"/>
+      <c r="C125" s="24"/>
+      <c r="D125" s="24"/>
+      <c r="E125" s="24"/>
       <c r="F125" s="13">
         <v>2</v>
       </c>
       <c r="G125" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H125" s="31"/>
-      <c r="I125" s="31"/>
-      <c r="J125" s="31"/>
-      <c r="K125" s="31"/>
-      <c r="L125" s="31"/>
+      <c r="H125" s="24"/>
+      <c r="I125" s="24"/>
+      <c r="J125" s="24"/>
+      <c r="K125" s="24"/>
+      <c r="L125" s="24"/>
       <c r="M125" s="13">
         <v>2</v>
       </c>
@@ -5478,20 +5486,20 @@
       <c r="B126" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C126" s="31"/>
-      <c r="D126" s="31"/>
-      <c r="E126" s="31"/>
+      <c r="C126" s="24"/>
+      <c r="D126" s="24"/>
+      <c r="E126" s="24"/>
       <c r="F126" s="13">
         <v>2</v>
       </c>
       <c r="G126" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="H126" s="31"/>
-      <c r="I126" s="31"/>
-      <c r="J126" s="31"/>
-      <c r="K126" s="31"/>
-      <c r="L126" s="31"/>
+      <c r="H126" s="24"/>
+      <c r="I126" s="24"/>
+      <c r="J126" s="24"/>
+      <c r="K126" s="24"/>
+      <c r="L126" s="24"/>
       <c r="M126" s="13">
         <v>2</v>
       </c>
@@ -5511,44 +5519,105 @@
       <c r="M127" s="13"/>
     </row>
     <row r="129" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B129" s="27" t="s">
+      <c r="B129" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="C129" s="27"/>
-      <c r="D129" s="27"/>
-      <c r="E129" s="27"/>
+      <c r="C129" s="28"/>
+      <c r="D129" s="28"/>
+      <c r="E129" s="28"/>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B130" s="27" t="s">
+      <c r="B130" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="C130" s="27"/>
-      <c r="D130" s="27"/>
-      <c r="E130" s="27"/>
-      <c r="J130" s="34"/>
-      <c r="K130" s="35"/>
-      <c r="L130" s="36"/>
+      <c r="C130" s="28"/>
+      <c r="D130" s="28"/>
+      <c r="E130" s="28"/>
+      <c r="J130" s="29"/>
+      <c r="K130" s="30"/>
+      <c r="L130" s="31"/>
     </row>
     <row r="131" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="27" t="s">
+      <c r="A131" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="B131" s="27"/>
-      <c r="C131" s="27"/>
-      <c r="D131" s="27"/>
-      <c r="E131" s="27"/>
-      <c r="F131" s="27"/>
-      <c r="G131" s="27"/>
-      <c r="H131" s="40" t="s">
+      <c r="B131" s="28"/>
+      <c r="C131" s="28"/>
+      <c r="D131" s="28"/>
+      <c r="E131" s="28"/>
+      <c r="F131" s="28"/>
+      <c r="G131" s="28"/>
+      <c r="H131" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="I131" s="41"/>
-      <c r="J131" s="37"/>
-      <c r="K131" s="38"/>
-      <c r="L131" s="39"/>
+      <c r="I131" s="36"/>
+      <c r="J131" s="32"/>
+      <c r="K131" s="33"/>
+      <c r="L131" s="34"/>
     </row>
   </sheetData>
-  <mergeCells count="78">
+  <mergeCells count="77">
+    <mergeCell ref="A6:A11"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="J89:M89"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="A13:A18"/>
+    <mergeCell ref="A20:A25"/>
+    <mergeCell ref="A27:A32"/>
+    <mergeCell ref="A34:A39"/>
+    <mergeCell ref="A41:A46"/>
+    <mergeCell ref="C101:E101"/>
+    <mergeCell ref="C95:E95"/>
+    <mergeCell ref="C96:E96"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="C93:E93"/>
+    <mergeCell ref="H93:L93"/>
+    <mergeCell ref="H94:L94"/>
+    <mergeCell ref="H95:L95"/>
+    <mergeCell ref="H96:L96"/>
+    <mergeCell ref="B130:E130"/>
+    <mergeCell ref="C106:E106"/>
+    <mergeCell ref="C107:E107"/>
+    <mergeCell ref="C108:E108"/>
+    <mergeCell ref="H99:L99"/>
+    <mergeCell ref="H100:L100"/>
+    <mergeCell ref="H101:L101"/>
+    <mergeCell ref="C102:E102"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="C105:E105"/>
+    <mergeCell ref="C99:E99"/>
+    <mergeCell ref="C100:E100"/>
+    <mergeCell ref="A131:G131"/>
+    <mergeCell ref="H102:L102"/>
+    <mergeCell ref="H105:L105"/>
+    <mergeCell ref="H106:L106"/>
+    <mergeCell ref="H107:L107"/>
+    <mergeCell ref="H108:L108"/>
+    <mergeCell ref="J130:L131"/>
+    <mergeCell ref="H131:I131"/>
+    <mergeCell ref="B129:E129"/>
+    <mergeCell ref="C111:E111"/>
+    <mergeCell ref="H111:L111"/>
+    <mergeCell ref="C112:E112"/>
+    <mergeCell ref="H112:L112"/>
+    <mergeCell ref="C113:E113"/>
+    <mergeCell ref="H113:L113"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="C114:E114"/>
+    <mergeCell ref="H114:L114"/>
+    <mergeCell ref="C120:E120"/>
+    <mergeCell ref="H120:L120"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="C117:E117"/>
+    <mergeCell ref="H117:L117"/>
+    <mergeCell ref="C118:E118"/>
+    <mergeCell ref="H118:L118"/>
     <mergeCell ref="C126:E126"/>
     <mergeCell ref="H126:L126"/>
     <mergeCell ref="A48:A53"/>
@@ -5565,68 +5634,6 @@
     <mergeCell ref="H125:L125"/>
     <mergeCell ref="C119:E119"/>
     <mergeCell ref="H119:L119"/>
-    <mergeCell ref="C114:E114"/>
-    <mergeCell ref="H114:L114"/>
-    <mergeCell ref="C120:E120"/>
-    <mergeCell ref="H120:L120"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="C117:E117"/>
-    <mergeCell ref="H117:L117"/>
-    <mergeCell ref="C118:E118"/>
-    <mergeCell ref="H118:L118"/>
-    <mergeCell ref="A131:G131"/>
-    <mergeCell ref="H102:L102"/>
-    <mergeCell ref="H105:L105"/>
-    <mergeCell ref="H106:L106"/>
-    <mergeCell ref="H107:L107"/>
-    <mergeCell ref="H108:L108"/>
-    <mergeCell ref="J130:L131"/>
-    <mergeCell ref="H131:I131"/>
-    <mergeCell ref="B129:E129"/>
-    <mergeCell ref="C111:E111"/>
-    <mergeCell ref="H111:L111"/>
-    <mergeCell ref="C112:E112"/>
-    <mergeCell ref="H112:L112"/>
-    <mergeCell ref="C113:E113"/>
-    <mergeCell ref="H113:L113"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="H93:L93"/>
-    <mergeCell ref="H94:L94"/>
-    <mergeCell ref="H95:L95"/>
-    <mergeCell ref="H96:L96"/>
-    <mergeCell ref="B130:E130"/>
-    <mergeCell ref="C106:E106"/>
-    <mergeCell ref="C107:E107"/>
-    <mergeCell ref="C108:E108"/>
-    <mergeCell ref="H99:L99"/>
-    <mergeCell ref="H100:L100"/>
-    <mergeCell ref="H101:L101"/>
-    <mergeCell ref="C102:E102"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="C105:E105"/>
-    <mergeCell ref="C99:E99"/>
-    <mergeCell ref="C100:E100"/>
-    <mergeCell ref="C101:E101"/>
-    <mergeCell ref="C95:E95"/>
-    <mergeCell ref="C96:E96"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="C93:E93"/>
-    <mergeCell ref="C94:E94"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="J89:M89"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="A13:A18"/>
-    <mergeCell ref="A20:A25"/>
-    <mergeCell ref="A27:A32"/>
-    <mergeCell ref="A34:A39"/>
-    <mergeCell ref="A41:A46"/>
-    <mergeCell ref="A6:A11"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:L3"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="86" orientation="portrait" r:id="rId1"/>
